--- a/data_CMS/CMS_109_TW4_2025.xlsx
+++ b/data_CMS/CMS_109_TW4_2025.xlsx
@@ -461,19 +461,19 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>KODE SATKER</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>KODE KANWIL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>KODE KPPN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>KODE SATKER</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>NAMA SATKER</t>
@@ -551,22 +551,22 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>TAHUN</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>TRIWULAN</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE_SHEET</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>KODE SATKER_RAW</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>TAHUN</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>TRIWULAN</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>SOURCE_SHEET</t>
         </is>
       </c>
     </row>
@@ -603,17 +603,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>403410</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>403410</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -679,22 +679,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>403410</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -731,17 +731,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>098963</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>098963</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -807,22 +807,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>098963</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>401945</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>401945</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -935,22 +935,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>401945</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -987,17 +987,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>401944</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1063,22 +1063,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>401944</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>402267</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1191,22 +1191,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>402267</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>099228</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>099228</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,22 +1319,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>099228</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -1371,17 +1371,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>007130</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1447,22 +1447,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>007130</t>
-        </is>
-      </c>
-      <c r="Z8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>007190</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>007190</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1575,22 +1575,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>007190</t>
-        </is>
-      </c>
-      <c r="Z9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -1627,98 +1627,98 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>007208</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>019301003871306</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>RKP KEJAKSAAN RI</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>654030072080000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>BPN 109 KN OK ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Inaktif CMS</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Inaktif Transaksi</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>007208</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>019301003871306</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>RKP KEJAKSAAN RI</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>654030072080000</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>BPN 109 KN OK ULU SELATAN</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Inaktif CMS</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Inaktif Transaksi</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>007208</t>
-        </is>
-      </c>
-      <c r="Z10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -1755,17 +1755,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>344894</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>344894</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1831,22 +1831,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>344894</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>685001</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1959,22 +1959,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>685001</t>
-        </is>
-      </c>
-      <c r="Z12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>410574</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>410574</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2087,22 +2087,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>410574</t>
-        </is>
-      </c>
-      <c r="Z13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2139,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>690801</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2215,22 +2215,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>690801</t>
-        </is>
-      </c>
-      <c r="Z14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2267,17 +2267,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>440505</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>440505</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2343,22 +2343,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>440505</t>
-        </is>
-      </c>
-      <c r="Z15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>666504</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>666504</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2471,22 +2471,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>666504</t>
-        </is>
-      </c>
-      <c r="Z16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2523,98 +2523,98 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>666506</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>023001004125308</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>RKK DITJEN BIMAS BUD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>651886665061000</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BPG 109 MENAG08 OKUT</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Inaktif CMS</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Inaktif Transaksi</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>666506</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>023001004125308</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>RKK DITJEN BIMAS BUD</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>651886665061000</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>BPG 109 MENAG08 OKUT</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Inaktif CMS</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Inaktif Transaksi</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>666506</t>
-        </is>
-      </c>
-      <c r="Z17" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2651,17 +2651,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>440502</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>440502</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2727,22 +2727,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>440502</t>
-        </is>
-      </c>
-      <c r="Z18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>666501</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>666501</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2855,22 +2855,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>666501</t>
-        </is>
-      </c>
-      <c r="Z19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -2907,17 +2907,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>418462</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>418462</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2983,22 +2983,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>418462</t>
-        </is>
-      </c>
-      <c r="Z20" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3035,17 +3035,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>418471</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>418471</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3111,22 +3111,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>418471</t>
-        </is>
-      </c>
-      <c r="Z21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>424245</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3239,22 +3239,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>424245</t>
-        </is>
-      </c>
-      <c r="Z22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3291,17 +3291,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>424967</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>424967</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3367,22 +3367,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>424967</t>
-        </is>
-      </c>
-      <c r="Z23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3419,17 +3419,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>426050</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>426050</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3495,22 +3495,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>426050</t>
-        </is>
-      </c>
-      <c r="Z24" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3547,17 +3547,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>426066</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>426066</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3623,22 +3623,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>426066</t>
-        </is>
-      </c>
-      <c r="Z25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3675,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>440504</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>440504</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3751,22 +3751,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>440504</t>
-        </is>
-      </c>
-      <c r="Z26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3803,17 +3803,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>553099</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>553099</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3879,22 +3879,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>553099</t>
-        </is>
-      </c>
-      <c r="Z27" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>574370</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>574370</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4007,22 +4007,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>574370</t>
-        </is>
-      </c>
-      <c r="Z28" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4059,17 +4059,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>597558</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>597558</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4135,22 +4135,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>597558</t>
-        </is>
-      </c>
-      <c r="Z29" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4187,17 +4187,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>661192</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>661192</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4263,22 +4263,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>661192</t>
-        </is>
-      </c>
-      <c r="Z30" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4315,17 +4315,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>666503</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>666503</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4391,22 +4391,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>666503</t>
-        </is>
-      </c>
-      <c r="Z31" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4443,17 +4443,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>597480</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>597480</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4519,22 +4519,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>597480</t>
-        </is>
-      </c>
-      <c r="Z32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4571,17 +4571,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>440503</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>440503</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4647,22 +4647,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>440503</t>
-        </is>
-      </c>
-      <c r="Z33" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4699,17 +4699,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>666502</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>666502</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4775,22 +4775,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>666502</t>
-        </is>
-      </c>
-      <c r="Z34" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4827,17 +4827,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>440507</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>440507</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4903,22 +4903,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>440507</t>
-        </is>
-      </c>
-      <c r="Z35" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -4955,17 +4955,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>666507</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>666507</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5031,22 +5031,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>666507</t>
-        </is>
-      </c>
-      <c r="Z36" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5083,17 +5083,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>440506</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>440506</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5159,22 +5159,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
         <is>
           <t>440506</t>
-        </is>
-      </c>
-      <c r="Z37" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5211,17 +5211,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>666505</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>666505</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5287,22 +5287,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>666505</t>
-        </is>
-      </c>
-      <c r="Z38" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5339,17 +5339,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>111071</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>111071</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5415,22 +5415,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>111071</t>
-        </is>
-      </c>
-      <c r="Z39" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5467,17 +5467,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>428258</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5543,22 +5543,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Y40" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>428258</t>
-        </is>
-      </c>
-      <c r="Z40" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5595,17 +5595,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>667215</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5671,22 +5671,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
         <is>
           <t>667215</t>
-        </is>
-      </c>
-      <c r="Z41" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>668529</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5799,22 +5799,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>668529</t>
-        </is>
-      </c>
-      <c r="Z42" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5851,17 +5851,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>669055</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>669055</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5927,22 +5927,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Y43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>669055</t>
-        </is>
-      </c>
-      <c r="Z43" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -5979,98 +5979,98 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>641681</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>019301003548301</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>RKK POLRI OPS</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>652376416811000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>BPG 109 POLRES OKU</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Inaktif CMS</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Inaktif Transaksi</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="Y44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>641681</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>POLRES OGAN KOMERING ULU</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>019301003548301</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>RKK POLRI OPS</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>652376416811000</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>BPG 109 POLRES OKU</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Inaktif CMS</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Inaktif Transaksi</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>641681</t>
-        </is>
-      </c>
-      <c r="Z44" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -6107,17 +6107,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>665292</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>665292</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6183,22 +6183,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>665292</t>
-        </is>
-      </c>
-      <c r="Z45" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -6235,17 +6235,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>665307</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6311,22 +6311,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Y46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>665307</t>
-        </is>
-      </c>
-      <c r="Z46" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -6363,17 +6363,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>111079</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6439,22 +6439,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Y47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>111079</t>
-        </is>
-      </c>
-      <c r="Z47" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -6491,17 +6491,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>656553</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6567,22 +6567,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Y48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>656553</t>
-        </is>
-      </c>
-      <c r="Z48" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -6619,17 +6619,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>656560</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6695,22 +6695,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Y49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>656560</t>
-        </is>
-      </c>
-      <c r="Z49" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -6747,17 +6747,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>419006</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>419006</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6823,22 +6823,22 @@
           <t>Tutup</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Y50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>419006</t>
-        </is>
-      </c>
-      <c r="Z50" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -6875,17 +6875,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>692334</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6951,22 +6951,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Y51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>692334</t>
-        </is>
-      </c>
-      <c r="Z51" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7003,17 +7003,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>692339</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7079,22 +7079,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Y52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
         <is>
           <t>692339</t>
-        </is>
-      </c>
-      <c r="Z52" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7131,17 +7131,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>692340</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>692340</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7207,22 +7207,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Y53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>692340</t>
-        </is>
-      </c>
-      <c r="Z53" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7259,17 +7259,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>692625</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7335,22 +7335,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Y54" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
         <is>
           <t>692625</t>
-        </is>
-      </c>
-      <c r="Z54" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7387,17 +7387,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>692725</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>692725</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7463,22 +7463,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Y55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>692725</t>
-        </is>
-      </c>
-      <c r="Z55" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7515,17 +7515,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>686503</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>686503</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7591,22 +7591,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Y56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
         <is>
           <t>686503</t>
-        </is>
-      </c>
-      <c r="Z56" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7643,17 +7643,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>691653</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>691653</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7719,22 +7719,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Y57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
         <is>
           <t>691653</t>
-        </is>
-      </c>
-      <c r="Z57" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7771,17 +7771,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>418457</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>418457</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7847,22 +7847,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Y58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
         <is>
           <t>418457</t>
-        </is>
-      </c>
-      <c r="Z58" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -7899,98 +7899,98 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>418460</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1030093939367</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>RKK DITJEN BIMAS HINDU KEMENAG OPS</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>8100124184601000</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>BPG 109 MENAG07 OKU</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Inaktif CMS</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Inaktif Transaksi</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="Y59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
         <is>
           <t>418460</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>1030093939367</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>RKK DITJEN BIMAS HINDU KEMENAG OPS</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>8100124184601000</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>BPG 109 MENAG07 OKU</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Inaktif CMS</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Inaktif Transaksi</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>418460</t>
-        </is>
-      </c>
-      <c r="Z59" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8027,17 +8027,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>418461</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>418461</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8103,22 +8103,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Y60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
         <is>
           <t>418461</t>
-        </is>
-      </c>
-      <c r="Z60" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8155,17 +8155,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>418458</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>418458</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8231,22 +8231,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Y61" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
         <is>
           <t>418458</t>
-        </is>
-      </c>
-      <c r="Z61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>402268</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>402268</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8359,22 +8359,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Y62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
         <is>
           <t>402268</t>
-        </is>
-      </c>
-      <c r="Z62" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8411,17 +8411,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>418459</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>418459</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8487,22 +8487,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Y63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
         <is>
           <t>418459</t>
-        </is>
-      </c>
-      <c r="Z63" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8539,17 +8539,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>418456</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>418456</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8615,22 +8615,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Y64" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
         <is>
           <t>418456</t>
-        </is>
-      </c>
-      <c r="Z64" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8667,17 +8667,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>431142</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>431142</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8743,22 +8743,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Y65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
         <is>
           <t>431142</t>
-        </is>
-      </c>
-      <c r="Z65" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8795,17 +8795,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>527975</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8871,22 +8871,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Y66" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
         <is>
           <t>527975</t>
-        </is>
-      </c>
-      <c r="Z66" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -8923,17 +8923,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>656574</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8999,22 +8999,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Y67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
         <is>
           <t>656574</t>
-        </is>
-      </c>
-      <c r="Z67" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -9051,17 +9051,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>670561</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>670561</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9127,22 +9127,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Y68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
         <is>
           <t>670561</t>
-        </is>
-      </c>
-      <c r="Z68" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -9179,17 +9179,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>553792</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>553792</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9255,22 +9255,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Y69" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
         <is>
           <t>553792</t>
-        </is>
-      </c>
-      <c r="Z69" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -9307,17 +9307,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>662127</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>662127</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9383,22 +9383,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Y70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
         <is>
           <t>662127</t>
-        </is>
-      </c>
-      <c r="Z70" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
@@ -9435,17 +9435,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>403409</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>06</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>403409</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9511,22 +9511,22 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Y71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>TW4</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>MASTER DATA</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
         <is>
           <t>403409</t>
-        </is>
-      </c>
-      <c r="Z71" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>TW4</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>MASTER DATA</t>
         </is>
       </c>
     </row>
